--- a/dataset/C2019-05 Fuel Tank Filter.xlsx
+++ b/dataset/C2019-05 Fuel Tank Filter.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="20910"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/jisantos_ubu_es/Documents/CodeDrive/GitHub/counterEVM-1/dataset/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_97029EF239CC8C1758F89AC99BC57D4F5E1E0C12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91F2D576-4007-465F-A062-E65314A527C4}"/>
   <bookViews>
-    <workbookView xWindow="30440" yWindow="0" windowWidth="25600" windowHeight="14420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline Schedule" sheetId="1" r:id="rId1"/>
     <sheet name="Gantt chart" sheetId="2" r:id="rId2"/>
     <sheet name="Resources" sheetId="3" r:id="rId3"/>
     <sheet name="Risk Analysis" sheetId="4" r:id="rId4"/>
-    <sheet name="Project Control - TP1" sheetId="5" r:id="rId5"/>
+    <sheet name="TP1" sheetId="5" r:id="rId5"/>
     <sheet name="TP2" sheetId="6" r:id="rId6"/>
     <sheet name="TP3" sheetId="7" r:id="rId7"/>
     <sheet name="TP4" sheetId="8" r:id="rId8"/>
@@ -966,10 +972,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\€"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\€"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1225,7 +1230,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1239,25 +1244,25 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1266,7 +1271,7 @@
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1292,13 +1297,10 @@
     <xf numFmtId="49" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1308,19 +1310,19 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="10" builtinId="9" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -1430,13 +1432,21 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1545,62 +1555,67 @@
             <c:numRef>
               <c:f>'Baseline Schedule'!$F$4:$F$20</c:f>
               <c:numCache>
-                <c:formatCode>dd/mm/yyyy\ h:mm</c:formatCode>
+                <c:formatCode>m/d/yyyy\ h:mm</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>42499.3333333333</c:v>
+                  <c:v>42499.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42520.3333333333</c:v>
+                  <c:v>42520.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>42688.3333333333</c:v>
+                  <c:v>42688.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>42656.3333333333</c:v>
+                  <c:v>42656.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42656.3333333333</c:v>
+                  <c:v>42656.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>42726.3333333333</c:v>
+                  <c:v>42726.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>42726.3333333333</c:v>
+                  <c:v>42726.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42656.3333333333</c:v>
+                  <c:v>42656.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>42656.3333333333</c:v>
+                  <c:v>42656.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>42726.3333333333</c:v>
+                  <c:v>42726.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>42726.3333333333</c:v>
+                  <c:v>42726.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42811.3333333333</c:v>
+                  <c:v>42811.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>42814.3333333333</c:v>
+                  <c:v>42814.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>43188.3333333333</c:v>
+                  <c:v>43188.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>43209.3333333333</c:v>
+                  <c:v>43209.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>43174.3333333333</c:v>
+                  <c:v>43174.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>43210.3333333333</c:v>
+                  <c:v>43210.333333333299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A82F-4A20-9282-A6F4F09F7973}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1618,6 +1633,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1628,6 +1648,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1638,6 +1663,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1648,6 +1678,11 @@
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1658,6 +1693,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1668,6 +1708,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000C-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1678,6 +1723,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000E-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1688,6 +1738,11 @@
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000010-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1698,6 +1753,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000012-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1708,6 +1768,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000014-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1718,6 +1783,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -1728,6 +1798,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000018-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -1738,6 +1813,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001A-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -1748,6 +1828,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001C-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -1758,6 +1843,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001E-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -1768,6 +1858,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000020-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -1778,6 +1873,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000022-A82F-4A20-9282-A6F4F09F7973}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1898,6 +1998,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000023-A82F-4A20-9282-A6F4F09F7973}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1950,8 +2055,8 @@
         <c:axId val="2109545336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="43210.70833333334"/>
-          <c:min val="42499.33333333334"/>
+          <c:max val="43210.708333333343"/>
+          <c:min val="42499.333333333343"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="t"/>
@@ -1996,9 +2101,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2084,42 +2189,47 @@
             <c:numRef>
               <c:f>'Tracking Overview'!$F$3:$F$12</c:f>
               <c:numCache>
-                <c:formatCode>###0.00\€</c:formatCode>
+                <c:formatCode>#,##0.00\€</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>268491.571643164</c:v>
+                  <c:v>268491.57164316397</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>424560.239857554</c:v>
+                  <c:v>424560.23985755403</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>535564.209235157</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>724799.352621689</c:v>
+                  <c:v>724799.35262168897</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>932866.585041907</c:v>
+                  <c:v>932866.58504190703</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>969034.148683728</c:v>
+                  <c:v>969034.14868372795</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0851564E6</c:v>
+                  <c:v>1085156.3999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0851564E6</c:v>
+                  <c:v>1085156.3999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.20939E6</c:v>
+                  <c:v>1209390</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.47629E6</c:v>
+                  <c:v>1476290</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9621-4B15-98C1-92A957AB60A5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2172,42 +2282,47 @@
             <c:numRef>
               <c:f>'Tracking Overview'!$E$3:$E$12</c:f>
               <c:numCache>
-                <c:formatCode>###0.00\€</c:formatCode>
+                <c:formatCode>#,##0.00\€</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>263831.578947368</c:v>
+                  <c:v>263831.57894736802</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>418322.173006774</c:v>
+                  <c:v>418322.17300677398</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>526138.567432531</c:v>
+                  <c:v>526138.56743253104</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>708316.400431633</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>903141.564678879</c:v>
+                  <c:v>903141.56467887899</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>939204.718262211</c:v>
+                  <c:v>939204.71826221095</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.04826E6</c:v>
+                  <c:v>1048260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.04826E6</c:v>
+                  <c:v>1048260</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1774E6</c:v>
+                  <c:v>1177400</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.456E6</c:v>
+                  <c:v>1456000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9621-4B15-98C1-92A957AB60A5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2260,42 +2375,47 @@
             <c:numRef>
               <c:f>'Tracking Overview'!$D$3:$D$12</c:f>
               <c:numCache>
-                <c:formatCode>###0.00\€</c:formatCode>
+                <c:formatCode>#,##0.00\€</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>249628.163808397</c:v>
+                  <c:v>249628.16380839699</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>523799.687553943</c:v>
+                  <c:v>523799.68755394302</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>765480.82466179</c:v>
+                  <c:v>765480.82466179004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>875862.019251879</c:v>
+                  <c:v>875862.01925187896</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>992375.502430306</c:v>
+                  <c:v>992375.50243030605</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.03856451945865E6</c:v>
+                  <c:v>1038564.51945865</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.05517858274978E6</c:v>
+                  <c:v>1055178.58274978</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.06480159713617E6</c:v>
+                  <c:v>1064801.5971361699</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.25055092592593E6</c:v>
+                  <c:v>1250550.92592593</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.456E6</c:v>
+                  <c:v>1456000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9621-4B15-98C1-92A957AB60A5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2305,7 +2425,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="2087437640"/>
         <c:axId val="2087443096"/>
@@ -2332,6 +2451,7 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2365,7 +2485,7 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
-        <c:numFmt formatCode="###0.00\€" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0.00\€" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2391,9 +2511,9 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2482,16 +2602,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.03676470588235</c:v>
+                  <c:v>1.0367647058823499</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.877118644067797</c:v>
+                  <c:v>0.87711864406779705</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.715725806451613</c:v>
+                  <c:v>0.71572580645161299</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.735099337748344</c:v>
+                  <c:v>0.73509933774834402</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.878133704735376</c:v>
@@ -2500,10 +2620,10 @@
                   <c:v>0.838476070528967</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.891595289079229</c:v>
+                  <c:v>0.89159528907922903</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.860278925619835</c:v>
+                  <c:v>0.86027892561983499</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.99248496993988</c:v>
@@ -2515,6 +2635,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F32B-495F-91DB-7318878601C6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2573,36 +2698,41 @@
                   <c:v>1.05689828792665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.798630054478018</c:v>
+                  <c:v>0.79863005447801805</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.687330825909314</c:v>
+                  <c:v>0.68733082590931405</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.808707747182192</c:v>
+                  <c:v>0.80870774718219196</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.910080471018385</c:v>
+                  <c:v>0.91008047101838496</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.904329678768314</c:v>
+                  <c:v>0.90432967876831405</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.993443211544583</c:v>
+                  <c:v>0.99344321154458304</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.98446508985274</c:v>
+                  <c:v>0.98446508985273995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.941505040371096</c:v>
+                  <c:v>0.94150504037109595</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F32B-495F-91DB-7318878601C6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2658,39 +2788,44 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.865169633772419</c:v>
+                  <c:v>0.86516963377241896</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.915761460566334</c:v>
+                  <c:v>0.91576146056633401</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.907106765458249</c:v>
+                  <c:v>0.90710676545824898</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.919496004872824</c:v>
+                  <c:v>0.91949600487282401</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.930493183553885</c:v>
+                  <c:v>0.93049318355388499</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.956007520972639</c:v>
+                  <c:v>0.95600752097263897</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.999605526025845</c:v>
+                  <c:v>0.99960552602584496</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.999605526025845</c:v>
+                  <c:v>0.99960552602584496</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.993127117672613</c:v>
+                  <c:v>0.99312711767261297</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F32B-495F-91DB-7318878601C6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2700,7 +2835,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="2109690312"/>
         <c:axId val="2109695768"/>
@@ -2727,6 +2861,7 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2802,7 +2937,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2837,7 +2978,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2872,7 +3019,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3174,96 +3327,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" customWidth="1"/>
-    <col min="10" max="12" width="10.6640625" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.6328125" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" customWidth="1"/>
+    <col min="3" max="3" width="5.6328125" customWidth="1"/>
+    <col min="4" max="5" width="16.6328125" customWidth="1"/>
+    <col min="6" max="7" width="13.6328125" customWidth="1"/>
+    <col min="8" max="8" width="8.6328125" customWidth="1"/>
+    <col min="9" max="9" width="25.6328125" customWidth="1"/>
+    <col min="10" max="12" width="10.6328125" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31" t="s">
+      <c r="J1" s="30"/>
+      <c r="K1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-    </row>
-    <row r="2" spans="1:17" ht="30" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+    </row>
+    <row r="2" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="30" t="s">
+      <c r="N2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -3298,7 +3451,7 @@
         <v>711.375</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3341,7 +3494,7 @@
         <v>311.375</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3384,7 +3537,7 @@
         <v>290.375</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="23">
+    <row r="6" spans="1:17" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3427,7 +3580,7 @@
         <v>39.375</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>18</v>
       </c>
@@ -3462,7 +3615,7 @@
         <v>407.375</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -3505,7 +3658,7 @@
         <v>372.375</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -3548,7 +3701,7 @@
         <v>309.375</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -3591,7 +3744,7 @@
         <v>337.375</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>19</v>
       </c>
@@ -3626,7 +3779,7 @@
         <v>414.375</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -3669,7 +3822,7 @@
         <v>349.375</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -3712,7 +3865,7 @@
         <v>281.375</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -3755,7 +3908,7 @@
         <v>344.375</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -3800,7 +3953,7 @@
         <v>376.375</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -3845,7 +3998,7 @@
         <v>359.375</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="23">
+    <row r="17" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -3890,7 +4043,7 @@
         <v>21.375</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -3935,7 +4088,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="23">
+    <row r="19" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -3980,7 +4133,7 @@
         <v>36.375</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -4042,24 +4195,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -4073,43 +4226,43 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4183,7 +4336,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -4233,7 +4386,7 @@
         <v>1038564.51945865</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -4305,7 +4458,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -4377,7 +4530,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -4449,7 +4602,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -4499,7 +4652,7 @@
         <v>241859.504132231</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -4571,7 +4724,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -4643,7 +4796,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -4715,7 +4868,7 @@
         <v>91859.504132231406</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -4765,7 +4918,7 @@
         <v>230105.26315789501</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -4837,7 +4990,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -4909,7 +5062,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -4981,7 +5134,7 @@
         <v>70105.263157894704</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -5053,7 +5206,7 @@
         <v>10933.085501858701</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -5125,7 +5278,7 @@
         <v>12666.666666666701</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -5195,7 +5348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -5265,7 +5418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -5335,7 +5488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -5423,24 +5576,24 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -5454,43 +5607,43 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -5564,7 +5717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -5614,7 +5767,7 @@
         <v>1055178.58274978</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -5686,7 +5839,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -5758,7 +5911,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -5830,7 +5983,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -5880,7 +6033,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -5952,7 +6105,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -6024,7 +6177,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -6096,7 +6249,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -6146,7 +6299,7 @@
         <v>234000</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -6218,7 +6371,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -6290,7 +6443,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -6362,7 +6515,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -6434,7 +6587,7 @@
         <v>15356.8773234201</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -6506,7 +6659,7 @@
         <v>17821.705426356599</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -6576,7 +6729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -6646,7 +6799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -6716,7 +6869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -6804,24 +6957,24 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -6835,43 +6988,43 @@
         <v>199</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -6945,7 +7098,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -6995,7 +7148,7 @@
         <v>1064801.5971361699</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -7067,7 +7220,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -7139,7 +7292,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -7211,7 +7364,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -7261,7 +7414,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -7333,7 +7486,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -7405,7 +7558,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -7477,7 +7630,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -7527,7 +7680,7 @@
         <v>234000</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -7599,7 +7752,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -7671,7 +7824,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -7743,7 +7896,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -7815,7 +7968,7 @@
         <v>16431.2267657993</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -7887,7 +8040,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -7957,7 +8110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -8027,7 +8180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -8097,7 +8250,7 @@
         <v>7370.3703703703704</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -8185,24 +8338,24 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -8216,43 +8369,43 @@
         <v>205</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -8326,7 +8479,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -8376,7 +8529,7 @@
         <v>1250550.92592593</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -8448,7 +8601,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -8520,7 +8673,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -8592,7 +8745,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -8642,7 +8795,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -8714,7 +8867,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -8786,7 +8939,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -8858,7 +9011,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -8908,7 +9061,7 @@
         <v>234000</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -8980,7 +9133,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -9052,7 +9205,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -9124,7 +9277,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -9196,7 +9349,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -9268,7 +9421,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -9340,7 +9493,7 @@
         <v>74625</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -9410,7 +9563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -9482,7 +9635,7 @@
         <v>117925.925925926</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -9570,24 +9723,24 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -9601,43 +9754,43 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -9711,7 +9864,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -9761,7 +9914,7 @@
         <v>1456000</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -9833,7 +9986,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -9905,7 +10058,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -9977,7 +10130,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -10027,7 +10180,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -10099,7 +10252,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -10171,7 +10324,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -10243,7 +10396,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -10293,7 +10446,7 @@
         <v>234000</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -10365,7 +10518,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -10437,7 +10590,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -10509,7 +10662,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -10581,7 +10734,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -10653,7 +10806,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -10725,7 +10878,7 @@
         <v>199000</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -10797,7 +10950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -10869,7 +11022,7 @@
         <v>199000</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -10959,29 +11112,29 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="D1" s="31" t="s">
+      <c r="B1" s="30"/>
+      <c r="D1" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="E1" s="31"/>
+      <c r="E1" s="30"/>
       <c r="G1" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>214</v>
       </c>
@@ -10995,7 +11148,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>216</v>
       </c>
@@ -11009,7 +11162,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>217</v>
       </c>
@@ -11023,7 +11176,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>218</v>
       </c>
@@ -11037,7 +11190,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>219</v>
       </c>
@@ -11051,7 +11204,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>220</v>
       </c>
@@ -11065,7 +11218,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>221</v>
       </c>
@@ -11079,7 +11232,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>222</v>
       </c>
@@ -11087,7 +11240,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>223</v>
       </c>
@@ -11095,7 +11248,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>225</v>
       </c>
@@ -11103,7 +11256,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -11111,7 +11264,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>227</v>
       </c>
@@ -11119,7 +11272,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>228</v>
       </c>
@@ -11127,7 +11280,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>229</v>
       </c>
@@ -11135,7 +11288,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>230</v>
       </c>
@@ -11143,7 +11296,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>231</v>
       </c>
@@ -11151,7 +11304,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>232</v>
       </c>
@@ -11159,7 +11312,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>233</v>
       </c>
@@ -11167,7 +11320,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>234</v>
       </c>
@@ -11175,7 +11328,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>235</v>
       </c>
@@ -11183,7 +11336,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>236</v>
       </c>
@@ -11191,7 +11344,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>237</v>
       </c>
@@ -11199,7 +11352,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>238</v>
       </c>
@@ -11207,7 +11360,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
         <v>239</v>
       </c>
@@ -11215,7 +11368,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="18" t="s">
         <v>240</v>
       </c>
@@ -11251,37 +11404,37 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:AI12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="14" width="15.6640625" customWidth="1"/>
-    <col min="15" max="31" width="17.6640625" customWidth="1"/>
+    <col min="1" max="14" width="15.6328125" customWidth="1"/>
+    <col min="15" max="31" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-    </row>
-    <row r="2" spans="1:35" ht="30" customHeight="1">
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+    </row>
+    <row r="2" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -11385,7 +11538,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>114</v>
       </c>
@@ -11489,7 +11642,7 @@
         <v>0.86516963377241896</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>124</v>
       </c>
@@ -11593,7 +11746,7 @@
         <v>0.91576146056633401</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>134</v>
       </c>
@@ -11697,7 +11850,7 @@
         <v>0.90710676545824898</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>151</v>
       </c>
@@ -11801,7 +11954,7 @@
         <v>0.91949600487282401</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>168</v>
       </c>
@@ -11905,7 +12058,7 @@
         <v>0.93049318355388499</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>182</v>
       </c>
@@ -12009,7 +12162,7 @@
         <v>0.95600752097263897</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>193</v>
       </c>
@@ -12113,7 +12266,7 @@
         <v>0.99960552602584496</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>199</v>
       </c>
@@ -12217,7 +12370,7 @@
         <v>0.99960552602584496</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>205</v>
       </c>
@@ -12321,7 +12474,7 @@
         <v>0.99312711767261297</v>
       </c>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>209</v>
       </c>
@@ -12442,9 +12595,9 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12457,9 +12610,9 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12472,25 +12625,25 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:M45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="32" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="E1" s="33"/>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="E1" s="32"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>6</v>
       </c>
@@ -12507,7 +12660,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>114</v>
       </c>
@@ -12524,7 +12677,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="27" t="s">
         <v>124</v>
       </c>
@@ -12541,7 +12694,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="27" t="s">
         <v>134</v>
       </c>
@@ -12558,7 +12711,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="27" t="s">
         <v>151</v>
       </c>
@@ -12575,7 +12728,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="27" t="s">
         <v>168</v>
       </c>
@@ -12592,7 +12745,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27" t="s">
         <v>182</v>
       </c>
@@ -12609,7 +12762,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27" t="s">
         <v>193</v>
       </c>
@@ -12626,7 +12779,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27" t="s">
         <v>199</v>
       </c>
@@ -12643,7 +12796,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="27" t="s">
         <v>205</v>
       </c>
@@ -12660,7 +12813,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="27" t="s">
         <v>209</v>
       </c>
@@ -12677,7 +12830,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="29"/>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -12692,7 +12845,7 @@
       <c r="L13" s="29"/>
       <c r="M13" s="29"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="29"/>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -12707,7 +12860,7 @@
       <c r="L14" s="29"/>
       <c r="M14" s="29"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="29"/>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
@@ -12722,7 +12875,7 @@
       <c r="L15" s="29"/>
       <c r="M15" s="29"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="29"/>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -12737,7 +12890,7 @@
       <c r="L16" s="29"/>
       <c r="M16" s="29"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="29"/>
       <c r="B17" s="29"/>
       <c r="C17" s="29"/>
@@ -12752,7 +12905,7 @@
       <c r="L17" s="29"/>
       <c r="M17" s="29"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="29"/>
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
@@ -12767,7 +12920,7 @@
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="29"/>
       <c r="B19" s="29"/>
       <c r="C19" s="29"/>
@@ -12782,7 +12935,7 @@
       <c r="L19" s="29"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="29"/>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -12797,7 +12950,7 @@
       <c r="L20" s="29"/>
       <c r="M20" s="29"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="29"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -12812,7 +12965,7 @@
       <c r="L21" s="29"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="29"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -12827,7 +12980,7 @@
       <c r="L22" s="29"/>
       <c r="M22" s="29"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="29"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -12842,7 +12995,7 @@
       <c r="L23" s="29"/>
       <c r="M23" s="29"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="29"/>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
@@ -12857,7 +13010,7 @@
       <c r="L24" s="29"/>
       <c r="M24" s="29"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="29"/>
       <c r="B25" s="29"/>
       <c r="C25" s="29"/>
@@ -12872,7 +13025,7 @@
       <c r="L25" s="29"/>
       <c r="M25" s="29"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="29"/>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -12887,7 +13040,7 @@
       <c r="L26" s="29"/>
       <c r="M26" s="29"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="29"/>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
@@ -12902,7 +13055,7 @@
       <c r="L27" s="29"/>
       <c r="M27" s="29"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="29"/>
       <c r="B28" s="29"/>
       <c r="C28" s="29"/>
@@ -12917,7 +13070,7 @@
       <c r="L28" s="29"/>
       <c r="M28" s="29"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="29"/>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -12932,7 +13085,7 @@
       <c r="L29" s="29"/>
       <c r="M29" s="29"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="29"/>
       <c r="B30" s="29"/>
       <c r="C30" s="29"/>
@@ -12947,7 +13100,7 @@
       <c r="L30" s="29"/>
       <c r="M30" s="29"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="29"/>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -12962,7 +13115,7 @@
       <c r="L31" s="29"/>
       <c r="M31" s="29"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="29"/>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -12977,7 +13130,7 @@
       <c r="L32" s="29"/>
       <c r="M32" s="29"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="29"/>
       <c r="B33" s="29"/>
       <c r="C33" s="29"/>
@@ -12992,7 +13145,7 @@
       <c r="L33" s="29"/>
       <c r="M33" s="29"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="29"/>
       <c r="B34" s="29"/>
       <c r="C34" s="29"/>
@@ -13007,7 +13160,7 @@
       <c r="L34" s="29"/>
       <c r="M34" s="29"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="29"/>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
@@ -13022,7 +13175,7 @@
       <c r="L35" s="29"/>
       <c r="M35" s="29"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="29"/>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
@@ -13037,7 +13190,7 @@
       <c r="L36" s="29"/>
       <c r="M36" s="29"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="29"/>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -13052,7 +13205,7 @@
       <c r="L37" s="29"/>
       <c r="M37" s="29"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="29"/>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
@@ -13067,7 +13220,7 @@
       <c r="L38" s="29"/>
       <c r="M38" s="29"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="29"/>
       <c r="B39" s="29"/>
       <c r="C39" s="29"/>
@@ -13082,7 +13235,7 @@
       <c r="L39" s="29"/>
       <c r="M39" s="29"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="29"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -13097,7 +13250,7 @@
       <c r="L40" s="29"/>
       <c r="M40" s="29"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="29"/>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
@@ -13112,7 +13265,7 @@
       <c r="L41" s="29"/>
       <c r="M41" s="29"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="29"/>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
@@ -13127,7 +13280,7 @@
       <c r="L42" s="29"/>
       <c r="M42" s="29"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="29"/>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -13142,7 +13295,7 @@
       <c r="L43" s="29"/>
       <c r="M43" s="29"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="29"/>
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
@@ -13157,7 +13310,7 @@
       <c r="L44" s="29"/>
       <c r="M44" s="29"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="29"/>
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
@@ -13187,9 +13340,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -13202,32 +13355,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="40.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="7" max="7" width="40.6328125" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="31"/>
-    </row>
-    <row r="2" spans="1:8" ht="25" customHeight="1">
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -13269,32 +13422,32 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="7" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="7" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -13317,7 +13470,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -13332,7 +13485,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="23">
+    <row r="4" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -13355,7 +13508,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="23">
+    <row r="5" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -13378,7 +13531,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="34">
+    <row r="6" spans="1:7" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -13401,7 +13554,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>18</v>
       </c>
@@ -13416,7 +13569,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -13439,7 +13592,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -13462,7 +13615,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -13485,7 +13638,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>19</v>
       </c>
@@ -13500,7 +13653,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -13523,7 +13676,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -13546,7 +13699,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -13569,7 +13722,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="23">
+    <row r="15" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -13592,7 +13745,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="23">
+    <row r="16" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -13615,7 +13768,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="23">
+    <row r="17" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -13638,7 +13791,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -13661,7 +13814,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="23">
+    <row r="19" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -13684,7 +13837,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -13722,24 +13875,24 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -13753,43 +13906,43 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -13863,7 +14016,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -13913,7 +14066,7 @@
         <v>249628.16380839699</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -13985,7 +14138,7 @@
         <v>116875</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -14057,7 +14210,7 @@
         <v>125894.73684210501</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -14127,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -14177,7 +14330,7 @@
         <v>3258.4269662921402</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -14247,7 +14400,7 @@
         <v>3258.4269662921402</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -14317,7 +14470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -14387,7 +14540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -14437,7 +14590,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -14509,7 +14662,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -14579,7 +14732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -14649,7 +14802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -14719,7 +14872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -14789,7 +14942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -14859,7 +15012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -14929,7 +15082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -14999,7 +15152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -15087,24 +15240,24 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -15118,43 +15271,43 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -15228,7 +15381,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -15278,7 +15431,7 @@
         <v>523799.68755394302</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -15350,7 +15503,7 @@
         <v>173839.285714286</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -15422,7 +15575,7 @@
         <v>196105.26315789501</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -15494,7 +15647,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -15544,7 +15697,7 @@
         <v>40567.737391026501</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -15614,7 +15767,7 @@
         <v>34756.554307116101</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -15684,7 +15837,7 @@
         <v>315.31531531531499</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -15754,7 +15907,7 @@
         <v>5495.8677685950397</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -15804,7 +15957,7 @@
         <v>43287.401290736401</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -15876,7 +16029,7 @@
         <v>38400</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -15948,7 +16101,7 @@
         <v>693.06930693069296</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -16018,7 +16171,7 @@
         <v>4194.3319838056696</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -16088,7 +16241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -16158,7 +16311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -16228,7 +16381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -16298,7 +16451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -16368,7 +16521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -16456,24 +16609,24 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -16487,43 +16640,43 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -16597,7 +16750,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -16647,7 +16800,7 @@
         <v>765480.82466179004</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -16719,7 +16872,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -16791,7 +16944,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -16863,7 +17016,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -16913,7 +17066,7 @@
         <v>108596.78975102901</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -16985,7 +17138,7 @@
         <v>73314.606741573007</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -17057,7 +17210,7 @@
         <v>1914.41441441441</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -17129,7 +17282,7 @@
         <v>33367.7685950413</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -17179,7 +17332,7 @@
         <v>110673.50783661399</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -17251,7 +17404,7 @@
         <v>81000</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -17323,7 +17476,7 @@
         <v>4207.9207920792096</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -17393,7 +17546,7 @@
         <v>25465.587044534401</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -17465,7 +17618,7 @@
         <v>1516.72862453532</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -17537,7 +17690,7 @@
         <v>1693.7984496124</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -17607,7 +17760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -17677,7 +17830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -17747,7 +17900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -17835,24 +17988,24 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -17866,43 +18019,43 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -17976,7 +18129,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -18026,7 +18179,7 @@
         <v>875862.01925187896</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -18098,7 +18251,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -18170,7 +18323,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -18242,7 +18395,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -18292,7 +18445,7 @@
         <v>160337.19577131199</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -18364,7 +18517,7 @@
         <v>102640.44943820201</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -18436,7 +18589,7 @@
         <v>3130.6306306306301</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -18508,7 +18661,7 @@
         <v>54566.115702479299</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -18558,7 +18711,7 @@
         <v>161924.91281516801</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -18630,7 +18783,7 @@
         <v>113400</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -18702,7 +18855,7 @@
         <v>6881.1881188118796</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -18772,7 +18925,7 @@
         <v>41643.724696356301</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -18844,7 +18997,7 @@
         <v>4929.3680297397796</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -18916,7 +19069,7 @@
         <v>5670.5426356589096</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -18986,7 +19139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -19056,7 +19209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -19126,7 +19279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -19214,24 +19367,24 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
@@ -19245,43 +19398,43 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-    </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+    </row>
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -19355,7 +19508,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -19405,7 +19558,7 @@
         <v>992375.50243030605</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="23">
+    <row r="6" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -19477,7 +19630,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="23">
+    <row r="7" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -19549,7 +19702,7 @@
         <v>253000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="34">
+    <row r="8" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -19621,7 +19774,7 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>18</v>
       </c>
@@ -19671,7 +19824,7 @@
         <v>214952.068792723</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -19743,7 +19896,7 @@
         <v>133595.50561797799</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -19815,7 +19968,7 @@
         <v>4414.4144144144102</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>6</v>
       </c>
@@ -19887,7 +20040,7 @@
         <v>76942.148760330601</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -19937,7 +20090,7 @@
         <v>216023.61807030899</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -20009,7 +20162,7 @@
         <v>147600</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -20081,7 +20234,7 @@
         <v>9702.9702970297003</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -20153,7 +20306,7 @@
         <v>58720.647773279401</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -20225,7 +20378,7 @@
         <v>8531.5985130111494</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -20297,7 +20450,7 @@
         <v>9868.2170542635595</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -20367,7 +20520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -20437,7 +20590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -20507,7 +20660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>

--- a/dataset/C2019-05 Fuel Tank Filter.xlsx
+++ b/dataset/C2019-05 Fuel Tank Filter.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="11_97029EF239CC8C1758F89AC99BC57D4F5E1E0C12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91F2D576-4007-465F-A062-E65314A527C4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13850" yWindow="120" windowWidth="24480" windowHeight="20760" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline Schedule" sheetId="1" r:id="rId1"/>
@@ -33,8 +33,19 @@
     <sheet name="SPI, SPI(t), p-factor" sheetId="18" r:id="rId18"/>
     <sheet name="Corrective actions Overview" sheetId="19" r:id="rId19"/>
   </sheets>
-  <calcPr calcId="124519" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -3043,6 +3054,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
